--- a/summary_stats/chuuchuu_summary_french.xlsx
+++ b/summary_stats/chuuchuu_summary_french.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,16 +474,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deutsche Bahn</t>
+          <t>Conseil Régional Auvergne - Rhône-Alpes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6760</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -495,13 +495,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3148</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1566</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6760</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -510,34 +510,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eurostar</t>
+          <t>Conseil Régional Auvergne - Rhône-Alpes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CTE</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42687</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>1775</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2646</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4421</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10547</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>6310</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>40397</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -546,34 +546,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>Conseil Régional Auvergne - Rhône-Alpes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INTERCITES</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18397</v>
+        <v>176</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>4136</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2697</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>18397</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -582,34 +582,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>Deutsche Bahn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INTERCITES DE NUIT</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2394</v>
+        <v>8289</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="H5" t="n">
-        <v>175</v>
+        <v>3776</v>
       </c>
       <c r="I5" t="n">
-        <v>123</v>
+        <v>1886</v>
       </c>
       <c r="J5" t="n">
-        <v>2394</v>
+        <v>8218</v>
       </c>
     </row>
     <row r="6">
@@ -618,34 +618,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>Eurostar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LYRIA</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8973</v>
+        <v>42687</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1775</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2646</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4421</v>
       </c>
       <c r="H6" t="n">
-        <v>1520</v>
+        <v>10548</v>
       </c>
       <c r="I6" t="n">
-        <v>842</v>
+        <v>6311</v>
       </c>
       <c r="J6" t="n">
-        <v>8973</v>
+        <v>40398</v>
       </c>
     </row>
     <row r="7">
@@ -654,16 +654,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>OCEdefault</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NAVETTE</t>
+          <t>CTE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>1537</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J7" t="n">
-        <v>47</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="8">
@@ -695,11 +695,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OUIGO</t>
+          <t>CAR TER</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16164</v>
+        <v>13630</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3290</v>
+        <v>1211</v>
       </c>
       <c r="I8" t="n">
-        <v>2015</v>
+        <v>233</v>
       </c>
       <c r="J8" t="n">
-        <v>16164</v>
+        <v>13630</v>
       </c>
     </row>
     <row r="9">
@@ -731,29 +731,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TGV INOUI</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>139731</v>
+        <v>3423</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>24885</v>
+        <v>730</v>
       </c>
       <c r="I9" t="n">
-        <v>13640</v>
+        <v>461</v>
       </c>
       <c r="J9" t="n">
-        <v>139728</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="10">
@@ -767,29 +767,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TRAIN TER</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>148494</v>
+        <v>504</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H10" t="n">
-        <v>11471</v>
+        <v>26</v>
       </c>
       <c r="I10" t="n">
-        <v>5665</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>148486</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11">
@@ -798,34 +798,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>INTERCITES</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4944</v>
+        <v>18995</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="H11" t="n">
-        <v>1104</v>
+        <v>4208</v>
       </c>
       <c r="I11" t="n">
-        <v>494</v>
+        <v>2723</v>
       </c>
       <c r="J11" t="n">
-        <v>4943</v>
+        <v>18687</v>
       </c>
     </row>
     <row r="12">
@@ -834,34 +834,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CAR TER</t>
+          <t>INTERCITES DE NUIT</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13630</v>
+        <v>2546</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H12" t="n">
-        <v>1211</v>
+        <v>187</v>
       </c>
       <c r="I12" t="n">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="J12" t="n">
-        <v>13630</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="13">
@@ -870,34 +870,682 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>LYR</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>209</v>
+      </c>
+      <c r="I13" t="n">
+        <v>107</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LYRIA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9467</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>152</v>
+      </c>
+      <c r="G14" t="n">
+        <v>156</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1583</v>
+      </c>
+      <c r="I14" t="n">
+        <v>875</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9401</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>801</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NAVETTE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>47</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OGO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3165</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37</v>
+      </c>
+      <c r="H17" t="n">
+        <v>574</v>
+      </c>
+      <c r="I17" t="n">
+        <v>331</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>27615</v>
+      </c>
+      <c r="E18" t="n">
+        <v>111</v>
+      </c>
+      <c r="F18" t="n">
+        <v>162</v>
+      </c>
+      <c r="G18" t="n">
+        <v>273</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4658</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2552</v>
+      </c>
+      <c r="J18" t="n">
+        <v>27444</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OUIGO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>17167</v>
+      </c>
+      <c r="E19" t="n">
+        <v>89</v>
+      </c>
+      <c r="F19" t="n">
+        <v>193</v>
+      </c>
+      <c r="G19" t="n">
+        <v>282</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3409</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2055</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17022</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>361586</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9002</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4331</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24416</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11060</v>
+      </c>
+      <c r="J20" t="n">
+        <v>350992</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TGV INOUI</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>145447</v>
+      </c>
+      <c r="E21" t="n">
+        <v>328</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1484</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1812</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25507</v>
+      </c>
+      <c r="I21" t="n">
+        <v>13824</v>
+      </c>
+      <c r="J21" t="n">
+        <v>144672</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TRAIN TER</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>148494</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11469</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5665</v>
+      </c>
+      <c r="J22" t="n">
+        <v>148494</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SNCF</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>TRAMTRAIN</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D23" t="n">
         <v>3250</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>77</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I23" t="n">
         <v>18</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J23" t="n">
         <v>3250</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SNCF VOYAGEURS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>856</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SNCF VOYAGEURS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CTE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>33252</v>
+      </c>
+      <c r="E25" t="n">
+        <v>27</v>
+      </c>
+      <c r="F25" t="n">
+        <v>155</v>
+      </c>
+      <c r="G25" t="n">
+        <v>182</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I25" t="n">
+        <v>327</v>
+      </c>
+      <c r="J25" t="n">
+        <v>33222</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SNCF VOYAGEURS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SNCF VOYAGEURS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3168</v>
+      </c>
+      <c r="E27" t="n">
+        <v>61</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12</v>
+      </c>
+      <c r="G27" t="n">
+        <v>73</v>
+      </c>
+      <c r="H27" t="n">
+        <v>145</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SNCF Voyageurs EA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CTE</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>83</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SNCF Voyageurs LO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2338</v>
+      </c>
+      <c r="E29" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29</v>
+      </c>
+      <c r="H29" t="n">
+        <v>107</v>
+      </c>
+      <c r="I29" t="n">
+        <v>53</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SNCF Voyageurs SA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CTE</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>22</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>11</v>
+      </c>
+      <c r="J30" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Trenitalia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4944</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1104</v>
+      </c>
+      <c r="I31" t="n">
+        <v>494</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4943</v>
       </c>
     </row>
   </sheetData>

--- a/summary_stats/chuuchuu_summary_french.xlsx
+++ b/summary_stats/chuuchuu_summary_french.xlsx
@@ -1545,7 +1545,7 @@
         <v>494</v>
       </c>
       <c r="J31" t="n">
-        <v>4943</v>
+        <v>4944</v>
       </c>
     </row>
   </sheetData>
